--- a/scripts/_bi_comparison.xlsx
+++ b/scripts/_bi_comparison.xlsx
@@ -949,9 +949,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>⚠ partial</t>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>campaigns_daily.spend always USD; _native cols for SAR</t>
+          <t>All BQ values in USD — no conversion needed in Hex</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Funnel workspace currency (SAR) caused SAR vs USD confusion</t>
+          <t>Funnel workspace currency (SAR) caused SAR vs USD confusion when comparing to Hex</t>
         </is>
       </c>
     </row>
